--- a/docentes/Flores Ovalle Victor - Estadisticos 20211.xlsx
+++ b/docentes/Flores Ovalle Victor - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -79,12 +79,6 @@
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MANZANET</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
@@ -97,12 +91,6 @@
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>LINARES</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
     <t>CABRERA</t>
   </si>
   <si>
@@ -116,12 +104,6 @@
   </si>
   <si>
     <t>JOSSELIN ANDREA</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>JADE EMILY</t>
   </si>
   <si>
     <t>YADIRA</t>
@@ -651,16 +633,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>61.29</v>
+      </c>
+      <c r="H2">
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -674,16 +659,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>67.73999999999999</v>
+      </c>
+      <c r="H3">
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -697,16 +685,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E4">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>76.47</v>
+      </c>
+      <c r="H4">
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -762,16 +753,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>67.73999999999999</v>
+        <v>74.19</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -788,16 +779,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>70.97</v>
+        <v>74.19</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -814,16 +805,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>76.47</v>
+        <v>79.41</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -833,7 +824,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -871,10 +862,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -883,7 +874,7 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -894,10 +885,10 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -906,21 +897,21 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920278</v>
+        <v>18330051920346</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -929,21 +920,21 @@
         <v>12</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920286</v>
+        <v>19330051920273</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -952,21 +943,21 @@
         <v>12</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>18330051920346</v>
+        <v>18330051920319</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -975,21 +966,21 @@
         <v>12</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920273</v>
+        <v>18330051920336</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -998,53 +989,7 @@
         <v>12</v>
       </c>
       <c r="G7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>18330051920319</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>18330051920336</v>
-      </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Flores Ovalle Victor - Estadisticos 20211.xlsx
+++ b/docentes/Flores Ovalle Victor - Estadisticos 20211.xlsx
@@ -79,24 +79,24 @@
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
     <t>DEGANTE</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
     <t>CABRERA</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
     <t>DOMINGUEZ</t>
   </si>
   <si>
@@ -106,10 +106,10 @@
     <t>JOSSELIN ANDREA</t>
   </si>
   <si>
+    <t>ESDRAS ALAN</t>
+  </si>
+  <si>
     <t>YADIRA</t>
-  </si>
-  <si>
-    <t>ESDRAS ALAN</t>
   </si>
   <si>
     <t>SHARITH</t>
@@ -902,7 +902,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>18330051920346</v>
+        <v>19330051920273</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
@@ -920,12 +920,12 @@
         <v>12</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920273</v>
+        <v>18330051920346</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
@@ -943,7 +943,7 @@
         <v>12</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">

--- a/docentes/Flores Ovalle Victor - Estadisticos 20211.xlsx
+++ b/docentes/Flores Ovalle Victor - Estadisticos 20211.xlsx
@@ -920,7 +920,7 @@
         <v>12</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">

--- a/docentes/Flores Ovalle Victor - Estadisticos 20211.xlsx
+++ b/docentes/Flores Ovalle Victor - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -76,46 +76,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
     <t>DEGANTE</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
     <t>DOMINGUEZ</t>
   </si>
   <si>
-    <t>BERNAL</t>
-  </si>
-  <si>
-    <t>JOSSELIN ANDREA</t>
-  </si>
-  <si>
-    <t>ESDRAS ALAN</t>
-  </si>
-  <si>
-    <t>YADIRA</t>
-  </si>
-  <si>
     <t>SHARITH</t>
-  </si>
-  <si>
-    <t>DIEGO OLLIN</t>
   </si>
 </sst>
 </file>
@@ -633,19 +600,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>61.29</v>
+        <v>74.19</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -659,19 +626,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>67.73999999999999</v>
+        <v>74.19</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -685,19 +652,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>76.47</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -753,16 +720,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>74.19</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -779,16 +746,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>74.19</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -805,16 +772,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>79.41</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -824,7 +791,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -856,139 +823,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920177</v>
+        <v>18330051920319</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>19330051920177</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>19330051920273</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>18330051920346</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>18330051920319</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>18330051920336</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
         <v>1</v>
       </c>
     </row>
